--- a/mmkBelgeler/KU009 CRM ezme tablosu.xlsx
+++ b/mmkBelgeler/KU009 CRM ezme tablosu.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myilmaz\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A0B997-16A0-E942-A5AA-7F8820B88B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="12390"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,9 +69,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -224,6 +225,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -590,14 +592,14 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -920,19 +922,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F144"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="28" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -952,7 +954,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -972,7 +974,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +994,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1012,7 +1014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1034,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1054,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1072,7 +1074,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1092,7 +1094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1114,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1152,7 +1154,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1172,7 +1174,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1194,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,7 +1214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,7 +1234,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,7 +1254,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1272,7 +1274,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +1314,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1354,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1372,7 +1374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1392,7 +1394,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +1414,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1434,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1452,7 +1454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +1474,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -1512,7 +1514,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -1532,7 +1534,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -1552,7 +1554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1574,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1594,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -1612,7 +1614,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1654,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
@@ -1692,7 +1694,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
@@ -1712,7 +1714,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
@@ -1732,7 +1734,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
@@ -1752,7 +1754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
@@ -1772,7 +1774,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>1</v>
       </c>
@@ -1792,7 +1794,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>1</v>
       </c>
@@ -1812,7 +1814,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
@@ -1832,7 +1834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>1</v>
       </c>
@@ -1852,7 +1854,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>1</v>
       </c>
@@ -1872,7 +1874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
@@ -1892,7 +1894,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>1</v>
       </c>
@@ -1912,7 +1914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>1</v>
       </c>
@@ -1932,7 +1934,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>1</v>
       </c>
@@ -1952,7 +1954,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>1</v>
       </c>
@@ -1972,7 +1974,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>1</v>
       </c>
@@ -1992,7 +1994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
@@ -2012,7 +2014,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>1</v>
       </c>
@@ -2032,7 +2034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>2</v>
       </c>
@@ -2052,7 +2054,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>2</v>
       </c>
@@ -2072,7 +2074,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>2</v>
       </c>
@@ -2092,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
@@ -2112,7 +2114,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>2</v>
       </c>
@@ -2132,7 +2134,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>2</v>
       </c>
@@ -2152,7 +2154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>2</v>
       </c>
@@ -2172,7 +2174,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>2</v>
       </c>
@@ -2192,7 +2194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>2</v>
       </c>
@@ -2212,7 +2214,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>2</v>
       </c>
@@ -2232,7 +2234,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>2</v>
       </c>
@@ -2252,7 +2254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>2</v>
       </c>
@@ -2272,7 +2274,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>2</v>
       </c>
@@ -2292,7 +2294,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>2</v>
       </c>
@@ -2312,7 +2314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>2</v>
       </c>
@@ -2332,7 +2334,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>2</v>
       </c>
@@ -2352,7 +2354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -2372,7 +2374,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -2392,7 +2394,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -2412,7 +2414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -2432,7 +2434,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -2452,7 +2454,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -2472,7 +2474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -2492,7 +2494,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -2512,7 +2514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -2532,7 +2534,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -2552,7 +2554,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -2572,7 +2574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -2592,7 +2594,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -2612,7 +2614,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -2652,7 +2654,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -2672,7 +2674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>4</v>
       </c>
@@ -2692,7 +2694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
         <v>4</v>
       </c>
@@ -2712,7 +2714,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
         <v>4</v>
       </c>
@@ -2732,7 +2734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>4</v>
       </c>
@@ -2752,7 +2754,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
         <v>4</v>
       </c>
@@ -2772,7 +2774,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
         <v>4</v>
       </c>
@@ -2792,7 +2794,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
         <v>4</v>
       </c>
@@ -2812,7 +2814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>4</v>
       </c>
@@ -2832,7 +2834,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
         <v>4</v>
       </c>
@@ -2852,7 +2854,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
         <v>4</v>
       </c>
@@ -2872,7 +2874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
         <v>4</v>
       </c>
@@ -2892,7 +2894,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
         <v>4</v>
       </c>
@@ -2912,7 +2914,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
         <v>4</v>
       </c>
@@ -2932,7 +2934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
         <v>4</v>
       </c>
@@ -2952,7 +2954,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
         <v>4</v>
       </c>
@@ -2972,7 +2974,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
         <v>4</v>
       </c>
@@ -2992,7 +2994,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
         <v>4</v>
       </c>
@@ -3012,7 +3014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
         <v>4</v>
       </c>
@@ -3032,7 +3034,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
         <v>4</v>
       </c>
@@ -3052,7 +3054,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
         <v>4</v>
       </c>
@@ -3072,7 +3074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
         <v>4</v>
       </c>
@@ -3092,7 +3094,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
         <v>4</v>
       </c>
@@ -3112,7 +3114,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
         <v>4</v>
       </c>
@@ -3132,7 +3134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
         <v>4</v>
       </c>
@@ -3152,7 +3154,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
         <v>4</v>
       </c>
@@ -3172,7 +3174,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
         <v>4</v>
       </c>
@@ -3192,7 +3194,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
         <v>4</v>
       </c>
@@ -3212,7 +3214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
         <v>4</v>
       </c>
@@ -3232,7 +3234,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
         <v>4</v>
       </c>
@@ -3252,7 +3254,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -3272,7 +3274,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -3292,7 +3294,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -3312,7 +3314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -3332,7 +3334,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -3352,7 +3354,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -3372,7 +3374,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -3392,7 +3394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -3412,7 +3414,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -3432,7 +3434,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -3452,7 +3454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -3472,7 +3474,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -3492,7 +3494,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -3512,7 +3514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -3532,7 +3534,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -3552,7 +3554,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -3572,7 +3574,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -3592,7 +3594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -3612,7 +3614,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3634,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -3652,7 +3654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -3672,7 +3674,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -3692,7 +3694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -3712,7 +3714,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -3732,7 +3734,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -3752,7 +3754,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -3772,7 +3774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -3792,7 +3794,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -3819,18 +3821,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mmkBelgeler/KU009 CRM ezme tablosu.xlsx
+++ b/mmkBelgeler/KU009 CRM ezme tablosu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A0B997-16A0-E942-A5AA-7F8820B88B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF97234-2158-B64C-B2B9-9EF51E6D3CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,28 +42,22 @@
     <t>S275JR</t>
   </si>
   <si>
-    <t>HR
-Grade</t>
+    <t>HR_Grade</t>
   </si>
   <si>
-    <t>Mamul
-Gnşlk Min</t>
+    <t>Mamul_Gns_Min</t>
   </si>
   <si>
-    <t>Mamul
-Gnşl Max</t>
+    <t>Mamul_Gns_Max</t>
   </si>
   <si>
-    <t>Mamul
-Klnlk Min</t>
+    <t>Mamul_Kln_Min</t>
   </si>
   <si>
-    <t>Mamul
-Klnlk Max</t>
+    <t>Mamul_Kln_Max</t>
   </si>
   <si>
-    <t>Giriş
-Kalınlığı</t>
+    <t>Giris_Kalinlik</t>
   </si>
 </sst>
 </file>
